--- a/creative-block/src/app/search/patterns/PatternListingDatabase.xlsx
+++ b/creative-block/src/app/search/patterns/PatternListingDatabase.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29721"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E43EBD75-CAB6-4246-9CF4-CDAF8F7D14EB}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Windows\System32\Team25_CreativeBlock\creative-block\src\app\search\patterns\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57AB258F-D973-4AC7-9765-42E35D7BC008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PatternListings" sheetId="1" r:id="rId1"/>
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t>Associated User</t>
   </si>
@@ -48,17 +53,65 @@
     <t>Rating</t>
   </si>
   <si>
-    <t>Approximate Time To Complete</t>
-  </si>
-  <si>
     <t>Materials Used</t>
+  </si>
+  <si>
+    <t>Difficulty</t>
+  </si>
+  <si>
+    <t>Craft Type</t>
+  </si>
+  <si>
+    <t>Pattern Type</t>
+  </si>
+  <si>
+    <t>Time To Complete</t>
+  </si>
+  <si>
+    <t>Download</t>
+  </si>
+  <si>
+    <t>adriennejuba</t>
+  </si>
+  <si>
+    <t>Magic Circle Tutorial</t>
+  </si>
+  <si>
+    <t>https://th.bing.com/th/id/OIP.l4_-PTjo2TwCQY8jmT2y4AHaE8?w=202&amp;h=135&amp;c=7&amp;r=0&amp;o=7&amp;dpr=1.5&amp;pid=1.7&amp;rm=3</t>
+  </si>
+  <si>
+    <t>Beginner</t>
+  </si>
+  <si>
+    <t>Crochet</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>5 minutes</t>
+  </si>
+  <si>
+    <t>Pattern Id</t>
+  </si>
+  <si>
+    <t>leebruton</t>
+  </si>
+  <si>
+    <t>Granny Square</t>
+  </si>
+  <si>
+    <t>https://th.bing.com/th/id/OIP.jBDv3noQ_OgKgEvovzdKJQHaHa?w=185&amp;h=185&amp;c=7&amp;r=0&amp;o=7&amp;dpr=1.5&amp;pid=1.7&amp;rm=3</t>
+  </si>
+  <si>
+    <t>15 minutes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,8 +140,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -107,9 +161,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -147,7 +201,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -253,7 +307,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -395,7 +449,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -403,39 +457,116 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1">
+        <v>46120</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="1">
+        <v>46120</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/creative-block/src/app/search/patterns/PatternListingDatabase.xlsx
+++ b/creative-block/src/app/search/patterns/PatternListingDatabase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Windows\System32\Team25_CreativeBlock\creative-block\src\app\search\patterns\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57AB258F-D973-4AC7-9765-42E35D7BC008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FD6ACF0-5E17-421C-B5C7-C853C905469C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="39">
   <si>
     <t>Associated User</t>
   </si>
@@ -105,6 +105,54 @@
   </si>
   <si>
     <t>15 minutes</t>
+  </si>
+  <si>
+    <t>orisullivan</t>
+  </si>
+  <si>
+    <t>Teddy Bear</t>
+  </si>
+  <si>
+    <t>https://th.bing.com/th/id/OIP.BQ6nJw6Tb4YXkDHnuGdAzwHaHa?w=206&amp;h=205&amp;c=7&amp;r=0&amp;o=5&amp;dpr=1.5&amp;pid=1.7</t>
+  </si>
+  <si>
+    <t>Intermediate</t>
+  </si>
+  <si>
+    <t>Toy</t>
+  </si>
+  <si>
+    <t>1 hour 30 minutes</t>
+  </si>
+  <si>
+    <t>Beanie</t>
+  </si>
+  <si>
+    <t>Clothing</t>
+  </si>
+  <si>
+    <t>3 hours</t>
+  </si>
+  <si>
+    <t>https://th.bing.com/th/id/OIP.o0NL6vZDE-LSc-x8sX6o1gHaJ4?w=164&amp;h=219&amp;c=7&amp;r=0&amp;o=5&amp;dpr=1.5&amp;pid=1.7</t>
+  </si>
+  <si>
+    <t>Bug Tapestry</t>
+  </si>
+  <si>
+    <t>https://th.bing.com/th/id/OIP.2bwq1bgFaOLo2q_CAsrmEAHaJ4?w=140&amp;h=187&amp;c=7&amp;r=0&amp;o=5&amp;dpr=1.5&amp;pid=1.7</t>
+  </si>
+  <si>
+    <t>Advanced</t>
+  </si>
+  <si>
+    <t>Knitting</t>
+  </si>
+  <si>
+    <t>Décor</t>
+  </si>
+  <si>
+    <t>10 hours</t>
   </si>
 </sst>
 </file>
@@ -457,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.08984375" bestFit="1" customWidth="1"/>
@@ -569,6 +617,93 @@
         <v>22</v>
       </c>
     </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="1">
+        <v>46121</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="1">
+        <v>46121</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="1">
+        <v>46121</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
